--- a/Result/profitability/2374.xlsx
+++ b/Result/profitability/2374.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.8</v>
       </c>
       <c r="M2" t="n">
-        <v>0.615</v>
+        <v>0.6575</v>
       </c>
       <c r="N2" t="n">
-        <v>24.4325</v>
+        <v>23.66</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.92</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.72375</v>
       </c>
       <c r="N3" t="n">
-        <v>21.84125</v>
+        <v>21.27125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.80875</v>
+        <v>0.87375</v>
       </c>
       <c r="N4" t="n">
-        <v>19.645</v>
+        <v>18.99</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.78</v>
+        <v>0.8325</v>
       </c>
       <c r="N5" t="n">
-        <v>17.07125</v>
+        <v>16.56375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8099999999999999</v>
+        <v>0.80125</v>
       </c>
       <c r="N6" t="n">
-        <v>14.99125</v>
+        <v>14.9075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.865</v>
+        <v>0.85125</v>
       </c>
       <c r="N7" t="n">
-        <v>13.345</v>
+        <v>13.645</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9537499999999999</v>
+        <v>0.965</v>
       </c>
       <c r="N8" t="n">
-        <v>12.10125</v>
+        <v>12.07</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2374</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3136</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2381</v>
+      </c>
+      <c r="E75" t="n">
+        <v>755</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="G75" t="n">
+        <v>328</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>351</v>
+      </c>
+      <c r="K75" t="n">
+        <v>275</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6174999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1232876712328768</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01027960526315785</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4199999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.059999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1443298969072164</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
